--- a/CBT_2024_4회/산업안전기사_2024_4회_문항등록.xlsx
+++ b/CBT_2024_4회/산업안전기사_2024_4회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1721,17 +1721,17 @@
       </c>
       <c r="AG5" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;다수를 한꺼번에 조직적으로 교육&lt;/strong&gt; 할 수 있는 것이 Off JT 의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT 와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT (직장 안)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT (직장 밖)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직장 실정에 맞다 · 개개인에 맞춘다 · 업무의 계속성이 끊기지 않는다 · 효과가 곧 나타난다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;훈련에만 전념 · 많은 사람을 한꺼번에 조직적으로 · 전문가 초빙 · 특별한 교재와 설비 · 여러 직장의 교류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;단점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;한 번에 많이 못 한다 · 상사의 능력에 좌우된다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;현장에 바로 맞지 않을 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;다수를 한꺼번에 조직적으로 교육&lt;/strong&gt;할 수 있는 것이 Off JT의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT (직장 안)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT (직장 밖)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직장 실정에 맞다 · 개개인에 맞춘다 · 업무의 계속성이 끊기지 않는다 · 효과가 곧 나타난다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;훈련에만 전념 · 많은 사람을 한꺼번에 조직적으로 · 전문가 초빙 · 특별한 교재와 설비 · 여러 직장의 교류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;단점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;한 번에 많이 못 한다 · 상사의 능력에 좌우된다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;현장에 바로 맞지 않을 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH5" s="32" t="inlineStr">
         <is>
-          <t>① 개개인에게 맞춘 지도훈련은 OJT 의 장점이다.&lt;br&gt;② 업무의 계속성이 끊기지 않는 것도 OJT 다.&lt;br&gt;④ 효과가 곧 업무에 나타나는 것도 OJT 다.</t>
+          <t>① 개개인에게 맞춘 지도훈련은 OJT의 장점이다.&lt;br&gt;② 업무의 계속성이 끊기지 않는 것도 OJT다.&lt;br&gt;④ 효과가 곧 업무에 나타나는 것도 OJT다.</t>
         </is>
       </c>
       <c r="AI5" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OJT 와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「많이 · 조직적으로 · 전문가 · 설비 · 교류」는 Off JT&lt;/strong&gt;, &lt;strong&gt;「맞춤 · 즉시 · 계속성」은 OJT&lt;/strong&gt;다. &lt;strong&gt;일터를 떠나면 그동안 일이 멈춘다&lt;/strong&gt;는 점에서 보기 ②는 OJT 쪽이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;다수를 조직적으로면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;OJT와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「많이 · 조직적으로 · 전문가 · 설비 · 교류」는 Off JT&lt;/strong&gt;, &lt;strong&gt;「맞춤 · 즉시 · 계속성」은 OJT&lt;/strong&gt;다. &lt;strong&gt;일터를 떠나면 그동안 일이 멈춘다&lt;/strong&gt;는 점에서 보기 ②는 OJT 쪽이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;다수를 조직적으로면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="AG7" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;누구나 자유롭게 말할 수&lt;/strong&gt; 있어야 한다. &lt;strong&gt;지정된 사람만 발언&lt;/strong&gt; 하는 것은 자유분방의 원칙에 어긋난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;브레인스토밍의 4원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기와의 대응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비판 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남의 생각을 깎아내리지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자유 분방&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;엉뚱해도 좋다 · 누구나 말한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②가 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대량 발언&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질보다 양&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수정 발언&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남의 생각에 얹거나 고쳐도 좋다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;누구나 자유롭게 말할 수&lt;/strong&gt; 있어야 한다. &lt;strong&gt;지정된 사람만 발언&lt;/strong&gt;하는 것은 자유분방의 원칙에 어긋난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;브레인스토밍의 4원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기와의 대응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비판 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남의 생각을 깎아내리지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자유 분방&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;엉뚱해도 좋다 · 누구나 말한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②가 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대량 발언&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질보다 양&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수정 발언&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남의 생각에 얹거나 고쳐도 좋다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH7" s="32" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="AI7" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;브레인스토밍의 4원칙&lt;/strong&gt;&lt;br&gt;네 원칙을 &lt;strong&gt;비 · 자 · 대 · 수&lt;/strong&gt;로 새긴다. 네 보기가 &lt;strong&gt;원칙 하나씩에 대응&lt;/strong&gt; 하도록 짜여 있어, 어느 하나가 어긋나는지만 보면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비판 금지 · 자유 분방 · 대량 발언 · 수정 발언&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;브레인스토밍의 4원칙&lt;/strong&gt;&lt;br&gt;네 원칙을 &lt;strong&gt;비 · 자 · 대 · 수&lt;/strong&gt;로 새긴다. 네 보기가 &lt;strong&gt;원칙 하나씩에 대응&lt;/strong&gt;하도록 짜여 있어, 어느 하나가 어긋나는지만 보면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비판 금지 · 자유 분방 · 대량 발언 · 수정 발언&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AG19" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;A · B · C · D 는 각 상해 갈래의 비보험 코스트 평균치&lt;/strong&gt;다. &lt;strong&gt;건수에 곱해 더하면 비보험 코스트 총액&lt;/strong&gt;이 나온다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;시몬즈 방식의 재해손실비&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보험 코스트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비보험 코스트&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;무엇&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산재보험료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보험으로 메워지지 않는 실제 손실&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;계산&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그대로 더한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;갈래별 평균치 × 건수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;네 갈래&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;휴업상해 · 통원상해 · 응급조치 · 무상해사고&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;A · B · C · D는 각 상해 갈래의 비보험 코스트 평균치&lt;/strong&gt;다. &lt;strong&gt;건수에 곱해 더하면 비보험 코스트 총액&lt;/strong&gt;이 나온다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;시몬즈 방식의 재해손실비&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보험 코스트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비보험 코스트&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;무엇&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산재보험료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보험으로 메워지지 않는 실제 손실&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;계산&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그대로 더한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;갈래별 평균치 × 건수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;네 갈래&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;휴업상해 · 통원상해 · 응급조치 · 무상해사고&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH19" s="32" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AI19" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시몬즈(Simonds)의 재해손실비 산정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보험 코스트는 그대로 더하고, 비보험 코스트는 갈래별 평균치에 건수를 곱해&lt;/strong&gt; 더한다. &lt;strong&gt;사망과 영구 전노동불능은 네 갈래에 들지 않는다&lt;/strong&gt; — 보험으로 크게 메워지기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;A·B·C·D 는 비보험 코스트 평균치&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;시몬즈(Simonds)의 재해손실비 산정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보험 코스트는 그대로 더하고, 비보험 코스트는 갈래별 평균치에 건수를 곱해&lt;/strong&gt; 더한다. &lt;strong&gt;사망과 영구 전노동불능은 네 갈래에 들지 않는다&lt;/strong&gt; — 보험으로 크게 메워지기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;A·B·C·D는 비보험 코스트 평균치&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="AG24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;조합 AND 게이트&lt;/strong&gt;다. &lt;strong&gt;입력 여러 개 가운데 정해진 수 이상이 일어나면&lt;/strong&gt; 출력이 난다는 조건이 옆의 육각형에 적힌다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 수정게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;언제 출력이 나나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;모양&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우선적 AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 정해진 순서대로 일어날 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;AND + 조건&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조합 AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 여러 개 중 정해진 수 이상이 일어날 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;AND + 조건 육각형&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배타적 OR 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 가운데 하나만 일어날 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;OR + 조건&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험지속 AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 일정 시간 이어질 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;AND + 조건&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건이 맞을 때만 입력을 출력으로 넘긴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;육각형 자체가 게이트&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;조합 AND 게이트&lt;/strong&gt;다. &lt;strong&gt;입력 여러 개 가운데 정해진 수 이상이 일어나면&lt;/strong&gt; 출력이 난다는 조건이 옆의 육각형에 적힌다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 수정게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;언제 출력이 나나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;모양&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우선적 AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 정해진 순서대로 일어날 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;AND + 조건&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조합 AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 여러 개 중 정해진 수 이상이 일어날 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;AND + 조건 육각형&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배타적 OR 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 가운데 하나만 일어날 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;OR + 조건&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험지속 AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 일정 시간 이어질 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;AND + 조건&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건이 맞을 때만 입력을 출력으로 넘긴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;육각형 자체가 게이트&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH24" s="32" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AI24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 수정게이트&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;그림의 몸통이 AND 모양(아래가 평평한 반원)인지 OR 모양(위가 둥근 방패꼴)인지&lt;/strong&gt;를 먼저 보고, &lt;strong&gt;옆에 붙은 육각형이 무슨 조건인지&lt;/strong&gt;로 갈린다. 이 그림은 &lt;strong&gt;AND 몸통 + 옆 조건&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AND 몸통에 옆 조건이면 조합 AND&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 수정게이트&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;그림의 몸통이 AND 모양(아래가 평평한 반원)인지 OR 모양(위가 둥근 방패꼴)인지&lt;/strong&gt;를 먼저 보고, &lt;strong&gt;옆에 붙은 육각형이 무슨 조건인지&lt;/strong&gt;로 갈린다. 이 그림은 &lt;strong&gt;AND 몸통 + 옆 조건&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AND 몸통에 옆 조건이면 조합 AND&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="U25" s="32" t="inlineStr">
         <is>
-          <t>FTA 에서 특정 조합의 기본사상들이 동시에 결함을 발생하였을 때 정상사상을 일으키는 기본사상의 집합을 무엇이라 하는가?</t>
+          <t>FTA에서 특정 조합의 기본사상들이 동시에 결함을 발생하였을 때 정상사상을 일으키는 기본사상의 집합을 무엇이라 하는가?</t>
         </is>
       </c>
       <c r="V25" s="32" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="AH25" s="32" t="inlineStr">
         <is>
-          <t>② 「error set」이라는 용어는 FTA 에 없다.&lt;br&gt;③ path set 은 정상사상이 일어나지 않게 하는 조합이다.&lt;br&gt;④ 「success set」이라는 용어도 없다.</t>
+          <t>② 「error set」이라는 용어는 FTA에 없다.&lt;br&gt;③ path set은 정상사상이 일어나지 않게 하는 조합이다.&lt;br&gt;④ 「success set」이라는 용어도 없다.</t>
         </is>
       </c>
       <c r="AI25" s="32" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="AH27" s="32" t="inlineStr">
         <is>
-          <t>① action 은 실행을 일으키는 이산적 제어다.&lt;br&gt;② selection 은 여럿 중 하나를 고르는 이산적 제어다.&lt;br&gt;④ data entry 는 값을 넣는 이산적 제어다.</t>
+          <t>① action은 실행을 일으키는 이산적 제어다.&lt;br&gt;② selection은 여럿 중 하나를 고르는 이산적 제어다.&lt;br&gt;④ data entry는 값을 넣는 이산적 제어다.</t>
         </is>
       </c>
       <c r="AI27" s="32" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AG29" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;노사 간 신뢰는 저하가 아니라 향상&lt;/strong&gt; 된다. 방향이 반대다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인간공학 적용의 기대효과&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;효과&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업자의 건강과 안전 향상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산재와 직업병 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업손실시간의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이직률과 결근율의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제품과 작업의 질 향상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;생산성 향상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;노사 간의 신뢰 향상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「저하」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;노사 간 신뢰는 저하가 아니라 향상&lt;/strong&gt;된다. 방향이 반대다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인간공학 적용의 기대효과&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;효과&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업자의 건강과 안전 향상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산재와 직업병 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업손실시간의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이직률과 결근율의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제품과 작업의 질 향상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;생산성 향상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;노사 간의 신뢰 향상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「저하」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH29" s="32" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="AI29" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인간공학의 기대효과&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;좋은 것은 늘고(질 · 안전 · 생산성 · 신뢰), 나쁜 것은 줄어야(산재 · 이직률 · 손실시간)&lt;/strong&gt; 한다. 보기 ①만 &lt;strong&gt;좋은 것을 줄인다&lt;/strong&gt;고 해 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;신뢰는 향상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인간공학의 기대효과&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;좋은 것은 늘고(질 · 안전 · 생산성 · 신뢰), 나쁜 것은 줄어야(산재 · 이직률 · 손실시간)&lt;/strong&gt;한다. 보기 ①만 &lt;strong&gt;좋은 것을 줄인다&lt;/strong&gt;고 해 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;신뢰는 향상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="AH30" s="32" t="inlineStr">
         <is>
-          <t>② ETA 는 초기 사건에서 시작하는 귀납적 기법이다.&lt;br&gt;③ FMEA 는 부품의 고장에서 시작하는 귀납적 기법이다.&lt;br&gt;④ HAZOP 은 가이드워드로 훑는 정성적 기법이다.</t>
+          <t>② ETA는 초기 사건에서 시작하는 귀납적 기법이다.&lt;br&gt;③ FMEA는 부품의 고장에서 시작하는 귀납적 기법이다.&lt;br&gt;④ HAZOP은 가이드워드로 훑는 정성적 기법이다.</t>
         </is>
       </c>
       <c r="AI30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA(결함수분석)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA 만 하향식·연역적&lt;/strong&gt;이고 나머지는 대체로 상향식·귀납적이다. &lt;strong&gt;「일반에서 개별로」가 연역, 「개별에서 일반으로」가 귀납&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA 는 하향식 연역&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA(결함수분석)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA 만 하향식·연역적&lt;/strong&gt;이고 나머지는 대체로 상향식·귀납적이다. &lt;strong&gt;「일반에서 개별로」가 연역, 「개별에서 일반으로」가 귀납&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA는 하향식 연역&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5313,17 +5313,17 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>$R = e^{-\lambda t}$ 에서 $0.95 = e^{-8 {,} 000 \lambda}$ 다. 양변에 자연로그를 취하면 $\ln 0.95 =-0.0513 =-8 {,} 000 \lambda$ 이므로 $\lambda = 6.4 \times 10^{-6}$ /시간이다.</t>
+          <t>$R = e^{-\lambda t}$에서 $0.95 = e^{-8 {,} 000 \lambda}$다. 양변에 자연로그를 취하면 $\ln 0.95 =-0.0513 =-8 {,} 000 \lambda$이므로 $\lambda = 6.4 \times 10^{-6}$ /시간이다.</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
         <is>
-          <t>① $3.4 \times 10^{-6}$ 는 계산과 맞지 않는다.&lt;br&gt;③ $8.2 \times 10^{-6}$ 도 맞지 않는다.&lt;br&gt;④ $9.5 \times 10^{-6}$ 도 맞지 않는다.</t>
+          <t>① $3.4 \times 10^{-6}$는 계산과 맞지 않는다.&lt;br&gt;③ $8.2 \times 10^{-6}$도 맞지 않는다.&lt;br&gt;④ $9.5 \times 10^{-6}$도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지수분포의 신뢰도&lt;/strong&gt;&lt;br&gt;$R = e^{-\lambda t}$ 를 뒤집으면 $\lambda =-\dfrac{\ln R}{t}$ 다. $\ln 0.95 \fallingdotseq - 0.0513$이라는 값만 알면 한 줄로 끝난다. &lt;strong&gt;평균수명 &lt;/strong&gt;$\mathrm{MTBF} = 1 / \lambda$도 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\lambda =-\ln R \div t$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;지수분포의 신뢰도&lt;/strong&gt;&lt;br&gt;$R = e^{-\lambda t}$를 뒤집으면 $\lambda =-\dfrac{\ln R}{t}$다. $\ln 0.95 \fallingdotseq - 0.0513$이라는 값만 알면 한 줄로 끝난다. &lt;strong&gt;평균수명 &lt;/strong&gt;$\mathrm{MTBF} = 1 / \lambda$도 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\lambda =-\ln R \div t$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="AH37" s="32" t="inlineStr">
         <is>
-          <t>① 3 ± 1 은 매직넘버가 아니다.&lt;br&gt;③ 10 ± 1 도 아니다.&lt;br&gt;④ 20 ± 2 도 아니다.</t>
+          <t>① 3 ± 1은 매직넘버가 아니다.&lt;br&gt;③ 10 ± 1 도 아니다.&lt;br&gt;④ 20 ± 2 도 아니다.</t>
         </is>
       </c>
       <c r="AI37" s="32" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="AH41" s="32" t="inlineStr">
         <is>
-          <t>① fail safe 는 고장이 나도 안전한 쪽으로 가게 하는 설계다.&lt;br&gt;② fool proof 는 모르고 잘못 다루어도 안전하게 하는 설계다.&lt;br&gt;③ lock out 은 정비 중 전원을 잠그는 절차다.</t>
+          <t>① fail safe는 고장이 나도 안전한 쪽으로 가게 하는 설계다.&lt;br&gt;② fool proof는 모르고 잘못 다루어도 안전하게 하는 설계다.&lt;br&gt;③ lock out은 정비 중 전원을 잠그는 절차다.</t>
         </is>
       </c>
       <c r="AI41" s="32" t="inlineStr">
@@ -6607,17 +6607,17 @@
       </c>
       <c r="AG43" s="32" t="inlineStr">
         <is>
-          <t>플랜지 지름은 &lt;strong&gt;숫돌 바깥지름의 1/3 이상&lt;/strong&gt;이므로 $300 \times 1 / 3 = 100$ [mm] 다.</t>
+          <t>플랜지 지름은 &lt;strong&gt;숫돌 바깥지름의 1/3 이상&lt;/strong&gt;이므로 $300 \times 1 / 3 = 100$ [mm]다.</t>
         </is>
       </c>
       <c r="AH43" s="32" t="inlineStr">
         <is>
-          <t>① 50 [mm] 는 1/6 로 기준에 못 미친다.&lt;br&gt;③ 150 [mm] 는 1/2 로 기준보다 크다.&lt;br&gt;④ 200 [mm] 는 2/3 로 훨씬 크다.</t>
+          <t>① 50 [mm]는 1/6로 기준에 못 미친다.&lt;br&gt;③ 150 [mm]는 1/2로 기준보다 크다.&lt;br&gt;④ 200 [mm]는 2/3로 훨씬 크다.</t>
         </is>
       </c>
       <c r="AI43" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;연삭숫돌의 플랜지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;플랜지는 숫돌 지름의 1/3 이상&lt;/strong&gt; 이라야 숫돌을 제대로 붙들어 파괴를 막는다. 연삭기는 이 밖에 &lt;strong&gt;작업 시작 전 1분, 숫돌 교체 뒤 3분 시운전&lt;/strong&gt;과 &lt;strong&gt;지름 5 [cm] 이상이면 덮개&lt;/strong&gt;가 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;플랜지는 숫돌 지름의 1/3 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;연삭숫돌의 플랜지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;플랜지는 숫돌 지름의 1/3 이상&lt;/strong&gt;이라야 숫돌을 제대로 붙들어 파괴를 막는다. 연삭기는 이 밖에 &lt;strong&gt;작업 시작 전 1분, 숫돌 교체 뒤 3분 시운전&lt;/strong&gt;과 &lt;strong&gt;지름 5 [cm] 이상이면 덮개&lt;/strong&gt;가 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;플랜지는 숫돌 지름의 1/3 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6736,17 +6736,17 @@
       </c>
       <c r="AG44" s="32" t="inlineStr">
         <is>
-          <t>$60 \times 1 / 3 = 20$ [cm] 다.</t>
+          <t>$60 \times 1 / 3 = 20$ [cm]다.</t>
         </is>
       </c>
       <c r="AH44" s="32" t="inlineStr">
         <is>
-          <t>① 10 [cm] 는 1/6 로 기준에 못 미친다.&lt;br&gt;③ 30 [cm] 는 1/2 로 기준보다 크다.&lt;br&gt;④ 60 [cm] 는 숫돌 지름 그대로다.</t>
+          <t>① 10 [cm]는 1/6로 기준에 못 미친다.&lt;br&gt;③ 30 [cm]는 1/2로 기준보다 크다.&lt;br&gt;④ 60 [cm]는 숫돌 지름 그대로다.</t>
         </is>
       </c>
       <c r="AI44" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;연삭숫돌의 플랜지&lt;/strong&gt;&lt;br&gt;41번과 같은 문항으로 단위만 다르다. &lt;strong&gt;1/3 이라는 비율&lt;/strong&gt;만 알면 [mm] 든 [cm] 든 그대로 나눈다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;플랜지는 숫돌 지름의 1/3 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;연삭숫돌의 플랜지&lt;/strong&gt;&lt;br&gt;41번과 같은 문항으로 단위만 다르다. &lt;strong&gt;1/3이라는 비율&lt;/strong&gt;만 알면 [mm] 든 [cm] 든 그대로 나눈다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;플랜지는 숫돌 지름의 1/3 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="AG45" s="32" t="inlineStr">
         <is>
-          <t>작은 물건은 &lt;strong&gt;플라이어가 아니라 바이스로 고정&lt;/strong&gt; 해야 한다. 손으로 쥐는 공구로 무는 순간 &lt;strong&gt;일감이 함께 돌아가며 손을 친다&lt;/strong&gt;.</t>
+          <t>작은 물건은 &lt;strong&gt;플라이어가 아니라 바이스로 고정&lt;/strong&gt;해야 한다. 손으로 쥐는 공구로 무는 순간 &lt;strong&gt;일감이 함께 돌아가며 손을 친다&lt;/strong&gt;.</t>
         </is>
       </c>
       <c r="AH45" s="32" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="AI45" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;드릴작업의 안전수칙&lt;/strong&gt;&lt;br&gt;원칙은 하나 — &lt;strong&gt;일감은 반드시 바이스나 클램프로 고정&lt;/strong&gt; 한다. &lt;strong&gt;손으로 잡거나 플라이어로 무는 것&lt;/strong&gt;은 모두 금지다. &lt;strong&gt;장갑을 끼지 않는다&lt;/strong&gt;도 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작은 일감은 바이스로 고정&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;드릴작업의 안전수칙&lt;/strong&gt;&lt;br&gt;원칙은 하나 — &lt;strong&gt;일감은 반드시 바이스나 클램프로 고정&lt;/strong&gt;한다. &lt;strong&gt;손으로 잡거나 플라이어로 무는 것&lt;/strong&gt;은 모두 금지다. &lt;strong&gt;장갑을 끼지 않는다&lt;/strong&gt;도 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작은 일감은 바이스로 고정&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="AG48" s="32" t="inlineStr">
         <is>
-          <t>사용응력은 $\dfrac{4 {,} 000}{6 \times 10} \fallingdotseq 66.7$ [kg/㎠] 이고, 허용응력은 $\dfrac{500}{5} = 100$ [kg/㎠] 다. 비는 $\dfrac{66.7}{100} \times 100 = 66.7$ [%] 다.</t>
+          <t>사용응력은 $\dfrac{4 {,} 000}{6 \times 10} \fallingdotseq 66.7$ [kg/㎠]이고, 허용응력은 $\dfrac{500}{5} = 100$ [kg/㎠]다. 비는 $\dfrac{66.7}{100} \times 100 = 66.7$ [%]다.</t>
         </is>
       </c>
       <c r="AH48" s="32" t="inlineStr">
         <is>
-          <t>① 33.3 [%] 는 계산과 맞지 않는다.&lt;br&gt;③ 99.5 [%] 도 맞지 않는다.&lt;br&gt;④ 250 [%] 는 허용응력을 넘어 성립하지 않는다.</t>
+          <t>① 33.3 [%]는 계산과 맞지 않는다.&lt;br&gt;③ 99.5 [%] 도 맞지 않는다.&lt;br&gt;④ 250 [%]는 허용응력을 넘어 성립하지 않는다.</t>
         </is>
       </c>
       <c r="AI48" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;사용응력과 허용응력&lt;/strong&gt;&lt;br&gt;두 값을 따로 구한 뒤 나눈다 — &lt;strong&gt;사용응력 = 하중 ÷ 단면적&lt;/strong&gt;, &lt;strong&gt;허용응력 = 강도 ÷ 안전율&lt;/strong&gt;. &lt;strong&gt;사용응력이 허용응력보다 작아야 안전&lt;/strong&gt; 하므로 100 [%] 를 넘는 보기는 곧바로 걸러진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;사용응력 ÷ 허용응력&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;사용응력과 허용응력&lt;/strong&gt;&lt;br&gt;두 값을 따로 구한 뒤 나눈다 — &lt;strong&gt;사용응력 = 하중 ÷ 단면적&lt;/strong&gt;, &lt;strong&gt;허용응력 = 강도 ÷ 안전율&lt;/strong&gt;. &lt;strong&gt;사용응력이 허용응력보다 작아야 안전&lt;/strong&gt;하므로 100 [%]를 넘는 보기는 곧바로 걸러진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;사용응력 ÷ 허용응력&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="AG49" s="32" t="inlineStr">
         <is>
-          <t>방진구는 &lt;strong&gt;일감의 길이가 지름의 12배 이상&lt;/strong&gt; 일 때 쓴다. &lt;strong&gt;짧은 일감에는 필요 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;선반 작업의 안전수칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;수칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;장갑·반지 등을 착용하지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;회전부에 말린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;칩은 기계를 세운 뒤 브러시로 제거한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가공물이 길면 심압대로 지지한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일감의 길이가 지름의 12배 이상이면 방진구를 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5배가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;칩 브레이커로 칩이 길게 이어지지 않게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>방진구는 &lt;strong&gt;일감의 길이가 지름의 12배 이상&lt;/strong&gt;일 때 쓴다. &lt;strong&gt;짧은 일감에는 필요 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;선반 작업의 안전수칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;수칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;장갑·반지 등을 착용하지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;회전부에 말린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;칩은 기계를 세운 뒤 브러시로 제거한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가공물이 길면 심압대로 지지한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일감의 길이가 지름의 12배 이상이면 방진구를 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5배가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;칩 브레이커로 칩이 길게 이어지지 않게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH49" s="32" t="inlineStr">
@@ -7510,17 +7510,17 @@
       </c>
       <c r="AG50" s="32" t="inlineStr">
         <is>
-          <t>풀리는 &lt;strong&gt;전동체&lt;/strong&gt;이므로 $Y = 6 + 0.15 X = 6 + 0.15 \times 50 = 13.5$ [mm] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가드 개구부 간격의 식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;적용&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 전동체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.15 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X &amp;lt; 160$&lt;u&gt; [mm] 일 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 비전동체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.1 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X &amp;lt; 760$&lt;u&gt; [mm] 일 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 30$&lt;u&gt; [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X \ge 160$ [mm] 이면&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>풀리는 &lt;strong&gt;전동체&lt;/strong&gt;이므로 $Y = 6 + 0.15 X = 6 + 0.15 \times 50 = 13.5$ [mm]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가드 개구부 간격의 식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;적용&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 전동체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.15 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X &amp;lt; 160$&lt;u&gt; [mm] 일 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 비전동체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.1 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X &amp;lt; 760$&lt;u&gt; [mm] 일 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 30$&lt;u&gt; [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X \ge 160$ [mm] 이면&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH50" s="32" t="inlineStr">
         <is>
-          <t>① 9.0 [mm] 는 계산과 맞지 않는다.&lt;br&gt;② 12.5 [mm] 도 맞지 않는다.&lt;br&gt;④ 25 [mm] 도 맞지 않는다.</t>
+          <t>① 9.0 [mm]는 계산과 맞지 않는다.&lt;br&gt;② 12.5 [mm] 도 맞지 않는다.&lt;br&gt;④ 25 [mm] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI50" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가드 개구부 간격(ISO 및 안전인증 기준)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;6 [mm] 는 손가락이 들어가지 못하는 최소값&lt;/strong&gt;이고, &lt;strong&gt;거리에 비례해 조금씩 넓혀 준다&lt;/strong&gt;. 계수는 &lt;strong&gt;전동체 0.15, 비전동체 0.1&lt;/strong&gt;로 &lt;strong&gt;전동체 쪽이 크다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전동체는 &lt;/u&gt;$6 + 0.15 X$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;가드 개구부 간격(ISO 및 안전인증 기준)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;6 [mm]는 손가락이 들어가지 못하는 최소값&lt;/strong&gt;이고, &lt;strong&gt;거리에 비례해 조금씩 넓혀 준다&lt;/strong&gt;. 계수는 &lt;strong&gt;전동체 0.15, 비전동체 0.1&lt;/strong&gt;로 &lt;strong&gt;전동체 쪽이 크다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전동체는 &lt;/u&gt;$6 + 0.15 X$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="AH51" s="32" t="inlineStr">
         <is>
-          <t>① 1.8 [m] 이내는 손 조작식의 위치다.&lt;br&gt;② 2.0 [m] 이내라는 기준은 없다.&lt;br&gt;④ 0.4 ~ 0.6 [m] 라는 범위도 없다.</t>
+          <t>① 1.8 [m] 이내는 손 조작식의 위치다.&lt;br&gt;② 2.0 [m] 이내라는 기준은 없다.&lt;br&gt;④ 0.4 ~ 0.6 [m]라는 범위도 없다.</t>
         </is>
       </c>
       <c r="AI51" s="32" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="AI52" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;광전자식 방호장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;광전자식은 「손이 들어오면 멈춘다」&lt;/strong&gt;는 장치라 &lt;strong&gt;멈출 수 있는 기계(마찰식 클러치)&lt;/strong&gt; 라야 뜻이 있다. &lt;strong&gt;핀 클러치(확동식)는 한 번 내려오면 못 멈춘다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;광전자식은 마찰식 클러치에만&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;광전자식 방호장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;광전자식은 「손이 들어오면 멈춘다」&lt;/strong&gt;는 장치라 &lt;strong&gt;멈출 수 있는 기계(마찰식 클러치)&lt;/strong&gt;라야 뜻이 있다. &lt;strong&gt;핀 클러치(확동식)는 한 번 내려오면 못 멈춘다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;광전자식은 마찰식 클러치에만&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8026,17 +8026,17 @@
       </c>
       <c r="AG54" s="32" t="inlineStr">
         <is>
-          <t>$D = 1.6 ( T_{l} + T_{s} )$ 에서 $96 = 1.6 \times ( 40 + T_{s} )$ 다. $40 + T_{s} = 60$ 이므로 $T_{s} = 20$ [ms] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;프레스 방호장치의 안전거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방호장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안전거리 식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;광전자식(감응식)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1.6 ( T_{l} + T_{s} )$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T$&lt;u&gt; 는 [ms]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1.6 ( T_{l} + T_{s} )$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수기동식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1.6 T_{m}$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T_{m} = ( 1 / 2 + \dfrac{1}{\text{클러치 맞물림 개소 수}} ) \times \dfrac{60 {,} 000}{\text{매분 행정수}}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손쳐내기식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 0.5 \times \text{행정길이}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$D = 1.6 ( T_{l} + T_{s} )$에서 $96 = 1.6 \times ( 40 + T_{s} )$다. $40 + T_{s} = 60$이므로 $T_{s} = 20$ [ms]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;프레스 방호장치의 안전거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방호장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안전거리 식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;광전자식(감응식)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1.6 ( T_{l} + T_{s} )$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T$&lt;u&gt;는 [ms]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1.6 ( T_{l} + T_{s} )$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수기동식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1.6 T_{m}$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T_{m} = ( 1 / 2 + \dfrac{1}{\text{클러치 맞물림 개소 수}} ) \times \dfrac{60 {,} 000}{\text{매분 행정수}}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손쳐내기식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 0.5 \times \text{행정길이}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH54" s="32" t="inlineStr">
         <is>
-          <t>① 15 [ms] 는 계산과 맞지 않는다.&lt;br&gt;③ 25 [ms] 도 맞지 않는다.&lt;br&gt;④ 30 [ms] 도 맞지 않는다.</t>
+          <t>① 15 [ms]는 계산과 맞지 않는다.&lt;br&gt;③ 25 [ms] 도 맞지 않는다.&lt;br&gt;④ 30 [ms] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI54" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;광전자식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1.6 은 사람 손이 움직이는 속도 1.6 [m/s]&lt;/strong&gt;에서 나왔다. &lt;strong&gt;[ms] 를 넣으면 [mm] 가 나오도록&lt;/strong&gt; 단위가 맞춰져 있어 환산이 필요 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $D = 1.6 ( T_{l} + T_{s} )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;광전자식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1.6은 사람 손이 움직이는 속도 1.6 [m/s]&lt;/strong&gt;에서 나왔다. &lt;strong&gt;[ms]를 넣으면 [mm]가 나오도록&lt;/strong&gt; 단위가 맞춰져 있어 환산이 필요 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $D = 1.6 ( T_{l} + T_{s} )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="AG55" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;감응시간을 조절하는 장치가 있어서는 안 된다&lt;/strong&gt;. 조절할 수 있으면 &lt;strong&gt;늦춰 놓아 무력화&lt;/strong&gt; 할 수 있기 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전매트의 일반구조&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구조&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단선경보장치가 부착되어 있을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;줄이 끊기면 알린다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;감응시간을 조절하는 장치가 부착되어 있지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「있어야 한다」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;감응도 조절장치가 있는 경우 봉인되어 있을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;함부로 못 바꾸게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;종류는 연결 사용 가능 여부에 따라 단일 감지기와 복합 감지기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;감응시간을 조절하는 장치가 있어서는 안 된다&lt;/strong&gt;. 조절할 수 있으면 &lt;strong&gt;늦춰 놓아 무력화&lt;/strong&gt;할 수 있기 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전매트의 일반구조&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구조&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단선경보장치가 부착되어 있을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;줄이 끊기면 알린다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;감응시간을 조절하는 장치가 부착되어 있지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「있어야 한다」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;감응도 조절장치가 있는 경우 봉인되어 있을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;함부로 못 바꾸게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;종류는 연결 사용 가능 여부에 따라 단일 감지기와 복합 감지기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH55" s="32" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="AI62" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;금형의 안전화&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;핀이 헐거우면 떨어진다&lt;/strong&gt;는 상식으로 걸러진다. &lt;strong&gt;억지 끼워맞춤(억지로 눌러 박는 것)&lt;/strong&gt; 이라야 빠지지 않는다. &lt;strong&gt;8 [mm] 는 손가락이 들어가지 못하는 크기&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;맞춤 핀은 억지 끼워맞춤&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;금형의 안전화&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;핀이 헐거우면 떨어진다&lt;/strong&gt;는 상식으로 걸러진다. &lt;strong&gt;억지 끼워맞춤(억지로 눌러 박는 것)&lt;/strong&gt;이라야 빠지지 않는다. &lt;strong&gt;8 [mm]는 손가락이 들어가지 못하는 크기&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;맞춤 핀은 억지 끼워맞춤&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="AG63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정격 표시&lt;/strong&gt;는 &lt;strong&gt;기기의 성능을 알리는 표시&lt;/strong&gt; 일 뿐 감전을 막지 못한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전 방지대책&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보호접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;새는 전류를 땅으로 보낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;누전차단기 설치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;새면 곧바로 끊는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연방호구 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;충전부와 사람 사이를 가로막는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이중절연기기 · 안전전압 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;애초에 위험을 없앤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정격 표시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성능을 알린다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감전 방지가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;정격 표시&lt;/strong&gt;는 &lt;strong&gt;기기의 성능을 알리는 표시&lt;/strong&gt;일 뿐 감전을 막지 못한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전 방지대책&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보호접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;새는 전류를 땅으로 보낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;누전차단기 설치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;새면 곧바로 끊는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연방호구 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;충전부와 사람 사이를 가로막는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이중절연기기 · 안전전압 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;애초에 위험을 없앤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정격 표시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성능을 알린다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감전 방지가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH63" s="32" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="AG65" s="32" t="inlineStr">
         <is>
-          <t>옛 기준으로 &lt;strong&gt;제3종 접지공사의 접지저항은 100 [Ω] 이하&lt;/strong&gt;다. 10 [Ω] 은 제1종의 값이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;옛 접지공사의 종별과 접지저항 (지금은 폐지)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종별&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접지저항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;적용&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제1종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고압·특고압 기기 외함 · 피뢰기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제2종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{150}{1 \text{선 지락전류}}$&lt;u&gt; [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;변압기 중성점&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제3종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;400 [V] 미만 저압 기기 외함&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;특별 제3종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;400 [V] 이상 저압 기기 외함&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>옛 기준으로 &lt;strong&gt;제3종 접지공사의 접지저항은 100 [Ω] 이하&lt;/strong&gt;다. 10 [Ω]은 제1종의 값이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;옛 접지공사의 종별과 접지저항 (지금은 폐지)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종별&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접지저항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;적용&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제1종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고압·특고압 기기 외함 · 피뢰기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제2종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{150}{1 \text{선 지락전류}}$&lt;u&gt; [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;변압기 중성점&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제3종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;400 [V] 미만 저압 기기 외함&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;특별 제3종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;400 [V] 이상 저압 기기 외함&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH65" s="32" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="AI65" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지락차단장치 설치의 예외 (옛 전기설비기술기준)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;제1종과 특별 제3종이 10 [Ω], 제3종이 100 [Ω]&lt;/strong&gt;이다. &lt;strong&gt;10 과 100 을 바꿔 놓는 것&lt;/strong&gt;이 이 유형의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제3종은 100 [Ω] 이하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 &lt;u&gt;제1·2·3종·특별 제3종이라는 접지공사 종별 구분이 폐지&lt;/u&gt; 되었다. 지금은 &lt;u&gt;접지시스템(계통접지·보호접지·피뢰시스템접지)&lt;/u&gt;으로 다시 짜였고, 지락차단장치 설치의 예외도 &lt;u&gt;KEC 211.2.4&lt;/u&gt;에 따로 규정되어 있다. 이 문항은 &lt;u&gt;옛 기준으로 푸는 문항&lt;/u&gt;이다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;지락차단장치 설치의 예외 (옛 전기설비기술기준)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;제1종과 특별 제3종이 10 [Ω], 제3종이 100 [Ω]&lt;/strong&gt;이다. &lt;strong&gt;10과 100을 바꿔 놓는 것&lt;/strong&gt;이 이 유형의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제3종은 100 [Ω] 이하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 &lt;u&gt;제1·2·3종·특별 제3종이라는 접지공사 종별 구분이 폐지&lt;/u&gt; 되었다. 지금은 &lt;u&gt;접지시스템(계통접지·보호접지·피뢰시스템접지)&lt;/u&gt;으로 다시 짜였고, 지락차단장치 설치의 예외도 &lt;u&gt;KEC 211.2.4&lt;/u&gt;에 따로 규정되어 있다. 이 문항은 &lt;u&gt;옛 기준으로 푸는 문항&lt;/u&gt;이다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9578,17 +9578,17 @@
       </c>
       <c r="AG66" s="32" t="inlineStr">
         <is>
-          <t>인체(3,000 [Ω])와 $R_{2}$(100 [Ω])의 병렬값은 $\dfrac{100 \times 3 {,} 000}{3 {,} 100} \fallingdotseq 96.8$ [Ω] 이다. 지락전류는 $200 / ( 10 + 96.8 ) \fallingdotseq 1.873$ [A] 이고, 인체로는 $1.873 \times \dfrac{100}{3 {,} 100} \fallingdotseq 0.0604$ [A] = &lt;strong&gt;60.4 [mA]&lt;/strong&gt;가 흐른다.</t>
+          <t>인체(3,000 [Ω])와 $R_{2}$(100 [Ω])의 병렬값은 $\dfrac{100 \times 3 {,} 000}{3 {,} 100} \fallingdotseq 96.8$ [Ω]이다. 지락전류는 $200 / ( 10 + 96.8 ) \fallingdotseq 1.873$ [A]이고, 인체로는 $1.873 \times \dfrac{100}{3 {,} 100} \fallingdotseq 0.0604$ [A] = &lt;strong&gt;60.4 [mA]&lt;/strong&gt;가 흐른다.</t>
         </is>
       </c>
       <c r="AH66" s="32" t="inlineStr">
         <is>
-          <t>② 30.21 [mA] 는 절반으로 계산한 값이다.&lt;br&gt;③ 15.11 [mA] 도 맞지 않는다.&lt;br&gt;④ 7.55 [mA] 도 맞지 않는다.</t>
+          <t>② 30.21 [mA]는 절반으로 계산한 값이다.&lt;br&gt;③ 15.11 [mA] 도 맞지 않는다.&lt;br&gt;④ 7.55 [mA] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI66" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지락 시 인체 통과 전류&lt;/strong&gt;&lt;br&gt;두 단계다 — &lt;strong&gt;전체 지락전류를 구하고, 그것을 인체와 &lt;/strong&gt;$R_{2}$&lt;strong&gt; 가 저항에 반비례해 나눠 가진다&lt;/strong&gt;. &lt;strong&gt;인체 저항이 훨씬 커서 대부분은 &lt;/strong&gt;$R_{2}$&lt;strong&gt; 로 흐르지만&lt;/strong&gt;, 남은 60 [mA] 만으로도 &lt;strong&gt;심실세동 영역&lt;/strong&gt;에 든다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전체 전류를 구하고 저항에 반비례해 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;지락 시 인체 통과 전류&lt;/strong&gt;&lt;br&gt;두 단계다 — &lt;strong&gt;전체 지락전류를 구하고, 그것을 인체와 &lt;/strong&gt;$R_{2}$&lt;strong&gt;가 저항에 반비례해 나눠 가진다&lt;/strong&gt;. &lt;strong&gt;인체 저항이 훨씬 커서 대부분은 &lt;/strong&gt;$R_{2}$&lt;strong&gt;로 흐르지만&lt;/strong&gt;, 남은 60 [mA] 만으로도 &lt;strong&gt;심실세동 영역&lt;/strong&gt;에 든다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전체 전류를 구하고 저항에 반비례해 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="AI67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;제2종 접지공사의 접지저항 (옛 전기설비기술기준)&lt;/strong&gt;&lt;br&gt;$\dfrac{150}{1 \text{선 지락전류}}$ 라는 식을 기억한다. &lt;strong&gt;고압이 저압으로 흘러넘쳤을 때 저압측 대지전압이 150 [V] 를 넘지 않게&lt;/strong&gt; 하려는 값이다. &lt;strong&gt;차단 시간에 따라 300 이나 600 을 쓰기도&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $150 \div 1 \text{선 지락전류}$.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 &lt;u&gt;접지공사 종별 구분이 폐지&lt;/u&gt; 되었다. 지금은 &lt;u&gt;계통접지(TN·TT·IT)&lt;/u&gt; 방식에 따라 정하며, &lt;u&gt;변압기 중성점 접지저항은 「고압·특고압측 전로 1선 지락전류로 150(또는 300·600)을 나눈 값 이하」&lt;/u&gt;라는 계산 원리가 &lt;u&gt;KEC 142.5&lt;/u&gt;에 그대로 남아 있다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;제2종 접지공사의 접지저항 (옛 전기설비기술기준)&lt;/strong&gt;&lt;br&gt;$\dfrac{150}{1 \text{선 지락전류}}$라는 식을 기억한다. &lt;strong&gt;고압이 저압으로 흘러넘쳤을 때 저압측 대지전압이 150 [V]를 넘지 않게&lt;/strong&gt; 하려는 값이다. &lt;strong&gt;차단 시간에 따라 300 이나 600을 쓰기도&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $150 \div 1 \text{선 지락전류}$.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 &lt;u&gt;접지공사 종별 구분이 폐지&lt;/u&gt; 되었다. 지금은 &lt;u&gt;계통접지(TN·TT·IT)&lt;/u&gt; 방식에 따라 정하며, &lt;u&gt;변압기 중성점 접지저항은 「고압·특고압측 전로 1선 지락전류로 150(또는 300·600)을 나눈 값 이하」&lt;/u&gt;라는 계산 원리가 &lt;u&gt;KEC 142.5&lt;/u&gt;에 그대로 남아 있다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AG68" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시동감도&lt;/strong&gt;는 &lt;strong&gt;아크를 낼 수 있는 2차측 최대저항&lt;/strong&gt;이다. &lt;strong&gt;값이 클수록 잘 시동되지만 너무 크면 사람 몸에도 반응&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;자동전격방지장치의 용어&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용어&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시동감도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아크를 낼 수 있는 2차측 최대저항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보통 500 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지동시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;용접봉을 뗀 뒤 무부하전압이 25 [V] 이하로 될 때까지의 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1초 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시동시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;용접봉을 대고 아크가 날 때까지의 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.06초 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무부하전압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아크를 쉴 때의 2차 전압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;25 ~ 30 [V] 이하&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;시동감도&lt;/strong&gt;는 &lt;strong&gt;아크를 낼 수 있는 2차측 최대저항&lt;/strong&gt;이다. &lt;strong&gt;값이 클수록 잘 시동되지만 너무 크면 사람 몸에도 반응&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;자동전격방지장치의 용어&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용어&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시동감도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아크를 낼 수 있는 2차측 최대저항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보통 500 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지동시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;용접봉을 뗀 뒤 무부하전압이 25 [V] 이하로 될 때까지의 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1초 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시동시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;용접봉을 대고 아크가 날 때까지의 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.06초 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무부하전압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아크를 쉴 때의 2차 전압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;25 ~ 30 [V] 이하&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH68" s="32" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="AI68" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자동전격방지장치의 시동감도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;시동감도가 지나치게 높으면 사람 몸(약 3,000 [Ω])에도 반응해 위험&lt;/strong&gt; 하므로 &lt;strong&gt;500 [Ω] 이하&lt;/strong&gt;로 제한한다. &lt;strong&gt;「감도」는 저항, 「시간」은 초&lt;/strong&gt;로 나뉜다는 점만 잡아도 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;시동감도는 2차측 최대저항&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자동전격방지장치의 시동감도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;시동감도가 지나치게 높으면 사람 몸(약 3,000 [Ω])에도 반응해 위험&lt;/strong&gt;하므로 &lt;strong&gt;500 [Ω] 이하&lt;/strong&gt;로 제한한다. &lt;strong&gt;「감도」는 저항, 「시간」은 초&lt;/strong&gt;로 나뉜다는 점만 잡아도 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;시동감도는 2차측 최대저항&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10086,17 +10086,17 @@
       </c>
       <c r="AG70" s="32" t="inlineStr">
         <is>
-          <t>$P = \sqrt{3} V I \cos \theta$ 에서 $I = \dfrac{P}{\sqrt{3} V \cos \theta} = \dfrac{50 {,} 000}{1.732 \times 380 \times 0.8} \fallingdotseq 94.96$ [A] 다.</t>
+          <t>$P = \sqrt{3} V I \cos \theta$에서 $I = \dfrac{P}{\sqrt{3} V \cos \theta} = \dfrac{50 {,} 000}{1.732 \times 380 \times 0.8} \fallingdotseq 94.96$ [A]다.</t>
         </is>
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>① 82.24 [A] 는 계산과 맞지 않는다.&lt;br&gt;③ 116.30 [A] 는 역률을 1 로 놓았을 때에 가깝다.&lt;br&gt;④ 164.47 [A] 는 √3 을 빠뜨렸을 때 나온다.</t>
+          <t>① 82.24 [A]는 계산과 맞지 않는다.&lt;br&gt;③ 116.30 [A]는 역률을 1로 놓았을 때에 가깝다.&lt;br&gt;④ 164.47 [A]는 √3을 빠뜨렸을 때 나온다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;3상 전력과 전류&lt;/strong&gt;&lt;br&gt;$P = \sqrt{3} V I \cos \theta$ 에서 &lt;strong&gt;√3 과 역률을 모두 나눈다&lt;/strong&gt;. &lt;strong&gt;둘 중 하나만 빠뜨려도 보기 ③ 이나 ④&lt;/strong&gt;로 빠지도록 짜여 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $I = P \div ( \sqrt{3} V \cos \theta )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;3상 전력과 전류&lt;/strong&gt;&lt;br&gt;$P = \sqrt{3} V I \cos \theta$에서 &lt;strong&gt;√3과 역률을 모두 나눈다&lt;/strong&gt;. &lt;strong&gt;둘 중 하나만 빠뜨려도 보기 ③ 이나 ④&lt;/strong&gt;로 빠지도록 짜여 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $I = P \div ( \sqrt{3} V \cos \theta )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10478,12 +10478,12 @@
       </c>
       <c r="AH73" s="32" t="inlineStr">
         <is>
-          <t>② 교류 30 [V], 직류 42 [V] 는 안전초저압의 값이 아니다.&lt;br&gt;③ 교류 30 [V], 직류 110 [V] 도 아니다.&lt;br&gt;④ 교류 50 [V], 직류 80 [V] 도 아니다.</t>
+          <t>② 교류 30 [V], 직류 42 [V]는 안전초저압의 값이 아니다.&lt;br&gt;③ 교류 30 [V], 직류 110 [V] 도 아니다.&lt;br&gt;④ 교류 50 [V], 직류 80 [V] 도 아니다.</t>
         </is>
       </c>
       <c r="AI73" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전초저압(SELV · PELV)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;교류 50 · 직류 120&lt;/strong&gt; 두 값을 짝으로 잡는다. &lt;strong&gt;직류가 더 높은 까닭은 같은 크기라도 직류가 덜 위험&lt;/strong&gt; 하기 때문이다. &lt;strong&gt;PELV 는 접지된 초저압&lt;/strong&gt;으로 SELV 와 값은 같다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;교류 50 [V], 직류 120 [V]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전초저압(SELV · PELV)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;교류 50 · 직류 120&lt;/strong&gt; 두 값을 짝으로 잡는다. &lt;strong&gt;직류가 더 높은 까닭은 같은 크기라도 직류가 덜 위험&lt;/strong&gt;하기 때문이다. &lt;strong&gt;PELV는 접지된 초저압&lt;/strong&gt;으로 SELV와 값은 같다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;교류 50 [V], 직류 120 [V]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="U74" s="32" t="inlineStr">
         <is>
-          <t>교류 아크용접기의 사용에서 무부하 전압이 80V, 아크 전압 25V, 아크 전류 300A일 경우 효율은 약 몇 % 인가? (단, 내부손실은 4kW 이다.)</t>
+          <t>교류 아크용접기의 사용에서 무부하 전압이 80V, 아크 전압 25V, 아크 전류 300A일 경우 효율은 약 몇 % 인가? (단, 내부손실은 4kW이다.)</t>
         </is>
       </c>
       <c r="V74" s="32" t="inlineStr"/>
@@ -10602,17 +10602,17 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>출력은 $25 \times 300 = 7 {,} 500$ [W] 다. 효율은 $\dfrac{\text{출력}}{\text{출력} + \text{내부손실}} \times 100 = \dfrac{7 {,} 500}{7 {,} 500 + 4 {,} 000} \times 100 \fallingdotseq 65.2$ [%] 다.</t>
+          <t>출력은 $25 \times 300 = 7 {,} 500$ [W]다. 효율은 $\dfrac{\text{출력}}{\text{출력} + \text{내부손실}} \times 100 = \dfrac{7 {,} 500}{7 {,} 500 + 4 {,} 000} \times 100 \fallingdotseq 65.2$ [%]다.</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>② 70.5 [%] 는 계산과 맞지 않는다.&lt;br&gt;③ 75.3 [%] 도 맞지 않는다.&lt;br&gt;④ 80.6 [%] 도 맞지 않는다.</t>
+          <t>② 70.5 [%]는 계산과 맞지 않는다.&lt;br&gt;③ 75.3 [%] 도 맞지 않는다.&lt;br&gt;④ 80.6 [%] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아크용접기의 효율&lt;/strong&gt;&lt;br&gt;$\text{효율} = \dfrac{\text{출력}}{\text{입력}} = \dfrac{\text{아크전압} \times \text{아크전류}}{\text{아크전압} \times \text{아크전류} + \text{내부손실}}$ 다. &lt;strong&gt;무부하전압 80 [V] 는 계산에 쓰이지 않는 미끼&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;출력 ÷ (출력 + 내부손실)&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;아크용접기의 효율&lt;/strong&gt;&lt;br&gt;$\text{효율} = \dfrac{\text{출력}}{\text{입력}} = \dfrac{\text{아크전압} \times \text{아크전류}}{\text{아크전압} \times \text{아크전류} + \text{내부손실}}$다. &lt;strong&gt;무부하전압 80 [V]는 계산에 쓰이지 않는 미끼&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;출력 ÷ (출력 + 내부손실)&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10731,17 +10731,17 @@
       </c>
       <c r="AG75" s="32" t="inlineStr">
         <is>
-          <t>옛 기준으로 &lt;strong&gt;400 [V] 이상은 0.4 [MΩ] 이상&lt;/strong&gt; 이라야 한다. 440 [V] 에서 0.3 [MΩ] 은 미달이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;옛 저압전로의 절연저항 기준 (지금은 폐지)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;절연저항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기와의 대응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대지전압 150 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.1 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①(110 [V], 0.14) 합격&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대지전압 150 [V] 초과 300 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.2 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②·④(220 [V], 0.25·0.2) 합격&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사용전압 300 [V] 초과 400 [V] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.3 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사용전압 400 [V] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.4 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③(440 [V], 0.3) 불합격&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>옛 기준으로 &lt;strong&gt;400 [V] 이상은 0.4 [MΩ] 이상&lt;/strong&gt;이라야 한다. 440 [V]에서 0.3 [MΩ]은 미달이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;옛 저압전로의 절연저항 기준 (지금은 폐지)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;절연저항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기와의 대응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대지전압 150 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.1 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①(110 [V], 0.14) 합격&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대지전압 150 [V] 초과 300 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.2 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②·④(220 [V], 0.25·0.2) 합격&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사용전압 300 [V] 초과 400 [V] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.3 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사용전압 400 [V] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.4 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③(440 [V], 0.3) 불합격&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH75" s="32" t="inlineStr">
         <is>
-          <t>① 110 [V] 회로의 0.14 [MΩ] 은 0.1 [MΩ] 이상이므로 합격이다.&lt;br&gt;② 220 [V] 회로의 0.25 [MΩ] 은 0.2 [MΩ] 이상이므로 합격이다.&lt;br&gt;④ 220 [V] 형광등 회로의 0.2 [MΩ] 도 기준에 맞는다.</t>
+          <t>① 110 [V] 회로의 0.14 [MΩ]은 0.1 [MΩ] 이상이므로 합격이다.&lt;br&gt;② 220 [V] 회로의 0.25 [MΩ]은 0.2 [MΩ] 이상이므로 합격이다.&lt;br&gt;④ 220 [V] 형광등 회로의 0.2 [MΩ] 도 기준에 맞는다.</t>
         </is>
       </c>
       <c r="AI75" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;저압전로의 절연저항 (옛 전기설비기술기준)&lt;/strong&gt;&lt;br&gt;네 값을 &lt;strong&gt;0.1 · 0.2 · 0.3 · 0.4&lt;/strong&gt;로 잡고, 경계를 &lt;strong&gt;150 · 300 · 400 [V]&lt;/strong&gt;로 짝지어 둔다. &lt;strong&gt;전압이 높을수록 더 큰 절연저항&lt;/strong&gt;을 요구한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0.1 · 0.2 · 0.3 · 0.4&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 절연저항 기준이 &lt;u&gt;세 줄로 단순해졌다&lt;/u&gt; — &lt;u&gt;SELV·PELV 는 0.5 [MΩ] 이상(시험전압 DC 250 [V]), FELV 와 500 [V] 이하는 1.0 [MΩ] 이상(DC 500 [V]), 500 [V] 초과는 1.0 [MΩ] 이상(DC 1,000 [V])&lt;/u&gt;. 옛 숫자(0.1 · 0.2 · 0.3 · 0.4)는 지금 쓰지 않는다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;저압전로의 절연저항 (옛 전기설비기술기준)&lt;/strong&gt;&lt;br&gt;네 값을 &lt;strong&gt;0.1 · 0.2 · 0.3 · 0.4&lt;/strong&gt;로 잡고, 경계를 &lt;strong&gt;150 · 300 · 400 [V]&lt;/strong&gt;로 짝지어 둔다. &lt;strong&gt;전압이 높을수록 더 큰 절연저항&lt;/strong&gt;을 요구한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0.1 · 0.2 · 0.3 · 0.4&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 절연저항 기준이 &lt;u&gt;세 줄로 단순해졌다&lt;/u&gt; — &lt;u&gt;SELV·PELV는 0.5 [MΩ] 이상(시험전압 DC 250 [V]), FELV와 500 [V] 이하는 1.0 [MΩ] 이상(DC 500 [V]), 500 [V] 초과는 1.0 [MΩ] 이상(DC 1,000 [V])&lt;/u&gt;. 옛 숫자(0.1 · 0.2 · 0.3 · 0.4)는 지금 쓰지 않는다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10870,7 @@
       </c>
       <c r="AI76" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;누전경보기의 구성&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;누전경보기는 「알리는」 설비이고, 누전차단기는 「끊는」 장치&lt;/strong&gt;다. &lt;strong&gt;변류기는 세 상의 전류 합이 0 이 아니면 누설이 있다&lt;/strong&gt;는 원리로 잡아낸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;변류기 + 수신부&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;누전경보기의 구성&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;누전경보기는 「알리는」 설비이고, 누전차단기는 「끊는」 장치&lt;/strong&gt;다. &lt;strong&gt;변류기는 세 상의 전류 합이 0이 아니면 누설이 있다&lt;/strong&gt;는 원리로 잡아낸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;변류기 + 수신부&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,11 @@
           <t>220 [V] 용 전동공구의 전원극과 외함 사이에 절연저항계를 대고 절연저항을 측정한다.</t>
         </is>
       </c>
-      <c r="W77" s="32" t="inlineStr"/>
+      <c r="W77" s="32" t="inlineStr">
+        <is>
+          <t>safe_A_2024_04_075_stem1.png</t>
+        </is>
+      </c>
       <c r="X77" s="32" t="inlineStr">
         <is>
           <t>0.1MΩ 이상</t>
@@ -10993,17 +10997,17 @@
       </c>
       <c r="AG77" s="32" t="inlineStr">
         <is>
-          <t>현행 KEC 로는 &lt;strong&gt;1.0 [MΩ] 이상&lt;/strong&gt;이다. 220 [V] 는 &lt;strong&gt;FELV 또는 500 [V] 이하&lt;/strong&gt; 구간에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;저압전로의 절연저항 (KEC 132)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전로의 사용전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;DC 시험전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;절연저항&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;SELV 및 PELV&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;250 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.5 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FELV, 500 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;500 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;500 [V] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>현행 KEC 로는 &lt;strong&gt;1.0 [MΩ] 이상&lt;/strong&gt;이다. 220 [V]는 &lt;strong&gt;FELV 또는 500 [V] 이하&lt;/strong&gt; 구간에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;저압전로의 절연저항 (KEC 132)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전로의 사용전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;DC 시험전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;절연저항&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;SELV 및 PELV&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;250 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.5 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FELV, 500 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;500 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;500 [V] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH77" s="32" t="inlineStr">
         <is>
-          <t>① 0.1 [MΩ] 은 옛 기준(대지전압 150 [V] 이하)의 값이다.&lt;br&gt;② 0.2 [MΩ] 은 옛 기준(300 [V] 이하)의 값이다.&lt;br&gt;③ 0.4 [MΩ] 은 옛 기준(400 [V] 이상)의 값이다.</t>
+          <t>① 0.1 [MΩ]은 옛 기준(대지전압 150 [V] 이하)의 값이다.&lt;br&gt;② 0.2 [MΩ]은 옛 기준(300 [V] 이하)의 값이다.&lt;br&gt;③ 0.4 [MΩ]은 옛 기준(400 [V] 이상)의 값이다.</t>
         </is>
       </c>
       <c r="AI77" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;한국전기설비규정(KEC) 132 — 전로의 절연저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;0.5 · 1.0 · 1.0&lt;/strong&gt; 세 값뿐이다. &lt;strong&gt;500 [V] 를 넘어도 절연저항은 1.0 [MΩ] 그대로&lt;/strong&gt;이고 &lt;strong&gt;시험전압만 1,000 [V] 로 올라간다&lt;/strong&gt;. 73번의 옛 기준과 견주어 두면 개정 전후가 함께 잡힌다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0.5 · 1.0 · 1.0&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;한국전기설비규정(KEC) 132 — 전로의 절연저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;0.5 · 1.0 · 1.0&lt;/strong&gt; 세 값뿐이다. &lt;strong&gt;500 [V]를 넘어도 절연저항은 1.0 [MΩ] 그대로&lt;/strong&gt;이고 &lt;strong&gt;시험전압만 1,000 [V]로 올라간다&lt;/strong&gt;. 73번의 옛 기준과 견주어 두면 개정 전후가 함께 잡힌다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0.5 · 1.0 · 1.0&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11643,12 +11647,12 @@
       </c>
       <c r="AH82" s="32" t="inlineStr">
         <is>
-          <t>② 에테르·이황화탄소 등은 4 [m/s] 가 아니라 1 [m/s] 이하다.&lt;br&gt;③ 비수용성 위험물은 5 [m/s] 가 아니라 1 [m/s] 이하다.&lt;br&gt;④ 저항률이 높은 위험물은 관 내경 0.1 [m] 일 때 2.5 [m/s] 이하다.</t>
+          <t>② 에테르·이황화탄소 등은 4 [m/s]가 아니라 1 [m/s] 이하다.&lt;br&gt;③ 비수용성 위험물은 5 [m/s]가 아니라 1 [m/s] 이하다.&lt;br&gt;④ 저항률이 높은 위험물은 관 내경 0.1 [m] 일 때 2.5 [m/s] 이하다.</t>
         </is>
       </c>
       <c r="AI82" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기 재해방지를 위한 유속 제한&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;전하가 잘 빠지는 도전성만 7 [m/s] 로 넉넉하고, 나머지는 1 [m/s] 안팎&lt;/strong&gt;으로 조인다. &lt;strong&gt;빠를수록 정전기가 많이 생긴다&lt;/strong&gt;는 것이 이 규정의 바탕이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;도전성만 7 [m/s], 나머지는 1 [m/s]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기 재해방지를 위한 유속 제한&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;전하가 잘 빠지는 도전성만 7 [m/s]로 넉넉하고, 나머지는 1 [m/s] 안팎&lt;/strong&gt;으로 조인다. &lt;strong&gt;빠를수록 정전기가 많이 생긴다&lt;/strong&gt;는 것이 이 규정의 바탕이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;도전성만 7 [m/s], 나머지는 1 [m/s]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11906,7 +11910,7 @@
       </c>
       <c r="AI84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자연발화의 방지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;자연발화의 정의 자체가 「점화원 없이」&lt;/strong&gt;다. 그러므로 &lt;strong&gt;점화원 관리는 자연발화 대책이 될 수 없다&lt;/strong&gt;. 대책은 &lt;strong&gt;열이 쌓이지 않게(온도 · 통풍 · 퇴적법)&lt;/strong&gt; 하는 쪽이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;점화원 없이 일어나므로 점화원 관리로는 못 막는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자연발화의 방지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;자연발화의 정의 자체가 「점화원 없이」&lt;/strong&gt;다. 그러므로 &lt;strong&gt;점화원 관리는 자연발화 대책이 될 수 없다&lt;/strong&gt;. 대책은 &lt;strong&gt;열이 쌓이지 않게(온도 · 통풍 · 퇴적법)&lt;/strong&gt;하는 쪽이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;점화원 없이 일어나므로 점화원 관리로는 못 막는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12541,12 +12545,12 @@
       </c>
       <c r="AG89" s="32" t="inlineStr">
         <is>
-          <t>$X \times Q = 1 {,} 100$ (일정)이므로 $X = \dfrac{1 {,} 100}{635.4} \fallingdotseq 1.73$ [vol%] 다.</t>
+          <t>$X \times Q = 1 {,} 100$ (일정)이므로 $X = \dfrac{1 {,} 100}{635.4} \fallingdotseq 1.73$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH89" s="32" t="inlineStr">
         <is>
-          <t>② 1.95 [%] 는 계산과 맞지 않는다.&lt;br&gt;③ 2.68 [%] 도 맞지 않는다.&lt;br&gt;④ 3.20 [%] 도 맞지 않는다.</t>
+          <t>② 1.95 [%]는 계산과 맞지 않는다.&lt;br&gt;③ 2.68 [%] 도 맞지 않는다.&lt;br&gt;④ 3.20 [%] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI89" s="32" t="inlineStr">
@@ -12674,17 +12678,17 @@
       </c>
       <c r="AG90" s="32" t="inlineStr">
         <is>
-          <t>에틸렌은 $n = 2$, $m = 4$ 이므로 $C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 ( 2 + 4 / 4 )} = \dfrac{100}{1 + 4.773 \times 3} = \dfrac{100}{15.32} \fallingdotseq 6.53$ [vol%] 다. 따라서 $\mathrm{LFL} = 0.55 \times 6.53 \fallingdotseq 3.6$ [vol%] 다.</t>
+          <t>에틸렌은 $n = 2$, $m = 4$이므로 $C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 ( 2 + 4 / 4 )} = \dfrac{100}{1 + 4.773 \times 3} = \dfrac{100}{15.32} \fallingdotseq 6.53$ [vol%]다. 따라서 $\mathrm{LFL} = 0.55 \times 6.53 \fallingdotseq 3.6$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH90" s="32" t="inlineStr">
         <is>
-          <t>① 0.55 는 식의 계수를 그대로 옮긴 값이다.&lt;br&gt;③ 6.3 은 화학양론조성 $C_{\mathrm{st}}$ 에 가까운 값이다.&lt;br&gt;④ 8.5 는 계산과 맞지 않는다.</t>
+          <t>① 0.55는 식의 계수를 그대로 옮긴 값이다.&lt;br&gt;③ 6.3은 화학양론조성 $C_{\mathrm{st}}$에 가까운 값이다.&lt;br&gt;④ 8.5는 계산과 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI90" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Jones 식과 화학양론조성&lt;/strong&gt;&lt;br&gt;두 단계다 — &lt;strong&gt;먼저 &lt;/strong&gt;$C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 ( n + m / 4 )}$&lt;strong&gt; 를 구하고, 0.55 를 곱한다&lt;/strong&gt;. &lt;strong&gt;상한계는 &lt;/strong&gt;$\mathrm{UFL} = 3.50 \times C_{\mathrm{st}}$로 구한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;LFL = 0.55 × &lt;/u&gt;$C_{\mathrm{st}}$&lt;u&gt;, UFL = 3.50 × &lt;/u&gt;$C_{\mathrm{st}}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;Jones 식과 화학양론조성&lt;/strong&gt;&lt;br&gt;두 단계다 — &lt;strong&gt;먼저 &lt;/strong&gt;$C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 ( n + m / 4 )}$&lt;strong&gt;를 구하고, 0.55를 곱한다&lt;/strong&gt;. &lt;strong&gt;상한계는 &lt;/strong&gt;$\mathrm{UFL} = 3.50 \times C_{\mathrm{st}}$로 구한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;LFL = 0.55 × &lt;/u&gt;$C_{\mathrm{st}}$&lt;u&gt;, UFL = 3.50 × &lt;/u&gt;$C_{\mathrm{st}}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12936,7 @@
       </c>
       <c r="AG92" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;질소&lt;/strong&gt;다. &lt;strong&gt;끓는점이 −196 [℃] 로 낮아 상온에서는 아무리 눌러도 액체가 되지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;고압가스의 분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;분류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압축가스&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상온에서 눌러도 기체 그대로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질소 · 산소 · 수소 · 아르곤 · 메탄&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;액화가스&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;눌러서 액체로 만든 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;프로판 · 부탄 · 염소 · 암모니아 · 산화에틸렌&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;용해가스&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;용제에 녹여 담은 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;질소&lt;/strong&gt;다. &lt;strong&gt;끓는점이 −196 [℃]로 낮아 상온에서는 아무리 눌러도 액체가 되지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;고압가스의 분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;분류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압축가스&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상온에서 눌러도 기체 그대로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질소 · 산소 · 수소 · 아르곤 · 메탄&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;액화가스&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;눌러서 액체로 만든 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;프로판 · 부탄 · 염소 · 암모니아 · 산화에틸렌&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;용해가스&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;용제에 녹여 담은 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH92" s="32" t="inlineStr">
@@ -13061,7 +13065,7 @@
       </c>
       <c r="AG93" s="32" t="inlineStr">
         <is>
-          <t>독성가스는 &lt;strong&gt;허용농도 이하&lt;/strong&gt;에서 울려야 한다. &lt;strong&gt;25 [%] 이하는 가연성가스(폭발하한계의 25 [%] 이하)&lt;/strong&gt;의 기준이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가스누출감지경보기의 경보설정값&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;경보설정값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가연성가스&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;폭발하한계의 25 [%] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;불붙기 훨씬 전에&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;독성가스&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;허용농도 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25 [%] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경보 정밀도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가연성 ±25 [%] 이하 · 독성 ±30 [%] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>독성가스는 &lt;strong&gt;허용농도 이하&lt;/strong&gt;에서 울려야 한다. &lt;strong&gt;25 [%] 이하는 가연성가스(폭발하한계의 25 [%] 이하)&lt;/strong&gt;의 기준이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가스누출감지경보기의 경보설정값&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;경보설정값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가연성가스&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;폭발하한계의 25 [%] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;불붙기 훨씬 전에&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;독성가스&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;허용농도 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25 [%]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경보 정밀도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가연성 ±25 [%] 이하 · 독성 ±30 [%] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH93" s="32" t="inlineStr">
@@ -13577,7 +13581,7 @@
       </c>
       <c r="AG97" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;표면연소&lt;/strong&gt;다. &lt;strong&gt;열분해나 증발 없이 고체 표면에서 산소와 바로 반응&lt;/strong&gt; 한다. &lt;strong&gt;불꽃 없이 빨갛게 달아오르는&lt;/strong&gt; 것이 특징이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;고체의 연소 형태&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;형태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;표면연소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;표면에서 바로 탄다 · 불꽃이 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;숯 · 코크스 · 목탄 · 금속분&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분해연소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;열분해로 나온 가스가 탄다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;목재 · 석탄 · 종이 · 플라스틱&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;증발연소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;녹아 증발한 증기가 탄다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;황 · 나프탈렌 · 파라핀&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자기연소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분자 속 산소로 스스로 탄다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;니트로셀룰로오스 · TNT&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;표면연소&lt;/strong&gt;다. &lt;strong&gt;열분해나 증발 없이 고체 표면에서 산소와 바로 반응&lt;/strong&gt;한다. &lt;strong&gt;불꽃 없이 빨갛게 달아오르는&lt;/strong&gt; 것이 특징이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;고체의 연소 형태&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;형태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;표면연소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;표면에서 바로 탄다 · 불꽃이 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;숯 · 코크스 · 목탄 · 금속분&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분해연소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;열분해로 나온 가스가 탄다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;목재 · 석탄 · 종이 · 플라스틱&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;증발연소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;녹아 증발한 증기가 탄다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;황 · 나프탈렌 · 파라핀&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자기연소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분자 속 산소로 스스로 탄다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;니트로셀룰로오스 · TNT&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH97" s="32" t="inlineStr">
@@ -13840,7 +13844,7 @@
       </c>
       <c r="AH99" s="32" t="inlineStr">
         <is>
-          <t>① 백드래프트는 산소가 모자란 실내에 공기가 들어와 폭발적으로 타는 현상이다.&lt;br&gt;③ 플래시오버는 실내 가연물이 한꺼번에 발화하는 현상이다.&lt;br&gt;④ UVCE 는 새어 나온 증기가 구름을 이룬 뒤 점화되는 폭발이다.</t>
+          <t>① 백드래프트는 산소가 모자란 실내에 공기가 들어와 폭발적으로 타는 현상이다.&lt;br&gt;③ 플래시오버는 실내 가연물이 한꺼번에 발화하는 현상이다.&lt;br&gt;④ UVCE는 새어 나온 증기가 구름을 이룬 뒤 점화되는 폭발이다.</t>
         </is>
       </c>
       <c r="AI99" s="32" t="inlineStr">
@@ -13930,7 +13934,7 @@
       </c>
       <c r="U100" s="32" t="inlineStr">
         <is>
-          <t>공기 중에서 이황화탄소(CS2)의 폭발한계는 하한값이 1.25vol%, 상한값이 44vol%이다. 이를 20℃ 대기압하에서 mg/L의 단위로 환산하면 하한값과 상한값은 각각 약 얼마인가? (단, 이황화탄소의 분자량은 76.1 이다.)</t>
+          <t>공기 중에서 이황화탄소(CS2)의 폭발한계는 하한값이 1.25vol%, 상한값이 44vol%이다. 이를 20℃ 대기압하에서 mg/L의 단위로 환산하면 하한값과 상한값은 각각 약 얼마인가? (단, 이황화탄소의 분자량은 76.1이다.)</t>
         </is>
       </c>
       <c r="V100" s="32" t="inlineStr"/>
@@ -13964,17 +13968,17 @@
       </c>
       <c r="AG100" s="32" t="inlineStr">
         <is>
-          <t>20 [℃] 의 몰부피는 $22.4 \times \dfrac{293}{273} \fallingdotseq 24.04$ [L] 다. $[ \mathrm{mg} / L ] = \dfrac{\mathrm{vol} \% \times 10 \times \text{분자량}}{24.04}$ 이므로 하한은 $\dfrac{1.25 \times 10 \times 76.1}{24.04} \fallingdotseq 39.6$, 상한은 $\dfrac{44 \times 10 \times 76.1}{24.04} \fallingdotseq 1 {,} 393$ [mg/L] 이다.</t>
+          <t>20 [℃]의 몰부피는 $22.4 \times \dfrac{293}{273} \fallingdotseq 24.04$ [L]다. $[ \mathrm{mg} / L ] = \dfrac{\mathrm{vol} \% \times 10 \times \text{분자량}}{24.04}$이므로 하한은 $\dfrac{1.25 \times 10 \times 76.1}{24.04} \fallingdotseq 39.6$, 상한은 $\dfrac{44 \times 10 \times 76.1}{24.04} \fallingdotseq 1 {,} 393$ [mg/L]이다.</t>
         </is>
       </c>
       <c r="AH100" s="32" t="inlineStr">
         <is>
-          <t>① 61 과 640 은 계산과 맞지 않는다.&lt;br&gt;③ 146 과 860 도 맞지 않는다.&lt;br&gt;④ 55.4 와 1,641.8 도 맞지 않는다.</t>
+          <t>① 61과 640은 계산과 맞지 않는다.&lt;br&gt;③ 146과 860 도 맞지 않는다.&lt;br&gt;④ 55.4와 1,641.8 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI100" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;[vol%] 와 [mg/L] 의 환산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;부피 비율을 질량 농도로 바꾸려면 분자량을 곱하고 몰부피로 나눈다&lt;/strong&gt;. &lt;strong&gt;20 [℃] 의 몰부피 24.04 [L]&lt;/strong&gt;를 쓰는 것이 갈림길이다 — &lt;strong&gt;0 [℃] 의 22.4 [L] 를 쓰면 값이 달라진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;20 [℃] 의 몰부피는 24.04 [L]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;[vol%]와 [mg/L]의 환산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;부피 비율을 질량 농도로 바꾸려면 분자량을 곱하고 몰부피로 나눈다&lt;/strong&gt;. &lt;strong&gt;20 [℃]의 몰부피 24.04 [L]&lt;/strong&gt;를 쓰는 것이 갈림길이다 — &lt;strong&gt;0 [℃]의 22.4 [L]를 쓰면 값이 달라진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;20 [℃]의 몰부피는 24.04 [L]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14356,7 +14360,7 @@
       </c>
       <c r="AH103" s="32" t="inlineStr">
         <is>
-          <t>① 4 [m] · 4 [m] 라는 기준은 없다.&lt;br&gt;③ 5.5 [m] · 7.5 [m] 는 통나무비계의 값이다.&lt;br&gt;④ 6 [m] · 8 [m] 는 틀비계의 값이다.</t>
+          <t>① 4 [m] · 4 [m]라는 기준은 없다.&lt;br&gt;③ 5.5 [m] · 7.5 [m]는 통나무비계의 값이다.&lt;br&gt;④ 6 [m] · 8 [m]는 틀비계의 값이다.</t>
         </is>
       </c>
       <c r="AI103" s="32" t="inlineStr">
@@ -14480,7 +14484,7 @@
       </c>
       <c r="AG104" s="32" t="inlineStr">
         <is>
-          <t>띠장 간격은 &lt;strong&gt;2.0 [m] 이하&lt;/strong&gt;다. 1 [m] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관비계의 숫자&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기와의 대응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격 — 띠장 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.85 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①이 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격 — 장선 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;띠장 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②가 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;묶어 세우는 구간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맨 윗부분에서 31 [m] 되는 지점 아래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③이 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간 적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;400 [kg] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④가 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>띠장 간격은 &lt;strong&gt;2.0 [m] 이하&lt;/strong&gt;다. 1 [m]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관비계의 숫자&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기와의 대응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격 — 띠장 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.85 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①이 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격 — 장선 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;띠장 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②가 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;묶어 세우는 구간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맨 윗부분에서 31 [m] 되는 지점 아래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③이 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간 적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;400 [kg] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④가 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH104" s="32" t="inlineStr">
@@ -14609,7 +14613,7 @@
       </c>
       <c r="AG105" s="32" t="inlineStr">
         <is>
-          <t>수직갱은 &lt;strong&gt;길이 15 [m] 이상일 때 10 [m] 이내마다&lt;/strong&gt; 계단참을 둔다. &lt;strong&gt;10 [m] / 7 [m] 가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;통로의 설치기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통로에는 75 [lux] 이상의 조명시설을 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①이 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통로의 주요한 부분에는 통로표시를 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②가 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경사가 15° 를 초과하면 미끄러지지 않는 구조로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④가 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수직갱에 가설된 통로가 길이 15 [m] 이상이면 10 [m] 이내마다 계단참을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③이 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 8 [m] 이상인 비계다리에는 7 [m] 이내마다 계단참을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7 [m] 는 여기에 쓰인다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>수직갱은 &lt;strong&gt;길이 15 [m] 이상일 때 10 [m] 이내마다&lt;/strong&gt; 계단참을 둔다. &lt;strong&gt;10 [m] / 7 [m]가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;통로의 설치기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통로에는 75 [lux] 이상의 조명시설을 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①이 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통로의 주요한 부분에는 통로표시를 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②가 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경사가 15° 를 초과하면 미끄러지지 않는 구조로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④가 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수직갱에 가설된 통로가 길이 15 [m] 이상이면 10 [m] 이내마다 계단참을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③이 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 8 [m] 이상인 비계다리에는 7 [m] 이내마다 계단참을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7 [m]는 여기에 쓰인다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH105" s="32" t="inlineStr">
@@ -15254,7 +15258,7 @@
       </c>
       <c r="AG110" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;토석의 강도가 오르면 오히려 더 안정&lt;/strong&gt; 된다. 붕괴 원인이 아니다.</t>
+          <t>&lt;strong&gt;토석의 강도가 오르면 오히려 더 안정&lt;/strong&gt;된다. 붕괴 원인이 아니다.</t>
         </is>
       </c>
       <c r="AH110" s="32" t="inlineStr">
@@ -15393,7 +15397,7 @@
       </c>
       <c r="AI111" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;히빙(heaving) 현상&lt;/strong&gt;&lt;br&gt;107번과 짝이다. &lt;strong&gt;「점토」와 「부풀어 오른다」&lt;/strong&gt; 두 낱말이 히빙을 가리킨다. &lt;strong&gt;heave 가 「부풀어 오르다」&lt;/strong&gt;라는 뜻이므로 이름 그대로다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;점토에서 바닥이 부풀면 히빙&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;히빙(heaving) 현상&lt;/strong&gt;&lt;br&gt;107번과 짝이다. &lt;strong&gt;「점토」와 「부풀어 오른다」&lt;/strong&gt; 두 낱말이 히빙을 가리킨다. &lt;strong&gt;heave가 「부풀어 오르다」&lt;/strong&gt;라는 뜻이므로 이름 그대로다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;점토에서 바닥이 부풀면 히빙&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15517,7 +15521,7 @@
       </c>
       <c r="AH112" s="32" t="inlineStr">
         <is>
-          <t>① 50 [%] 는 공정률 50 ~ 70 [%] 구간의 기준이다.&lt;br&gt;② 60 [%] 라는 기준은 없다.&lt;br&gt;④ 90 [%] 는 공정률 90 [%] 이상 구간의 기준이다.</t>
+          <t>① 50 [%]는 공정률 50 ~ 70 [%] 구간의 기준이다.&lt;br&gt;② 60 [%]라는 기준은 없다.&lt;br&gt;④ 90 [%]는 공정률 90 [%] 이상 구간의 기준이다.</t>
         </is>
       </c>
       <c r="AI112" s="32" t="inlineStr">
@@ -15780,7 +15784,7 @@
       </c>
       <c r="AI114" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제56조 — 작업발판의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;한 점만 고정하면 그 점을 축으로 돌아간다&lt;/strong&gt; — 그래서 &lt;strong&gt;둘 이상&lt;/strong&gt; 이라야 한다. &lt;strong&gt;「하나 이상」과 「둘 이상」&lt;/strong&gt;을 바꿔 놓는 것이 이 유형의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;둘 이상의 지지물에 고정&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C56%EC%A1%B0" target="_blank"&gt;제56조(작업발판의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 비계(달비계, 달대비계 및 말비계는 제외한다)의 높이가 2미터 이상인 작업장소에 다음 각 호의 기준에 맞는 작업발판을 설치하여야 한다. &amp;lt;개정 2012.5.31, 2017.12.28&amp;gt;&lt;br&gt; 1. 발판재료는 작업할 때의 하중을 견딜 수 있도록 견고한 것으로 할 것&lt;br&gt; 2. 작업발판의 폭은 40센티미터 이상으로 하고, 발판재료 간의 틈은 3센티미터 이하로 할 것. 다만, 외줄비계의 경우에는 고용노동부장관이 별도로 정하는 기준에 따른다.&lt;br&gt; 3. 제2호에도 불구하고 선박 및 보트 건조작업의 경우 선박블록 또는 엔진실 등의 좁은 작업공간에 작업발판을 설치하기 위하여 필요하면 작업발판의 폭을 30센티미터 이상으로 할 수 있고, 걸침비계의 경우 강관기둥 때문에 발판재료 간의 틈을 3센티미터 이하로 유지하기 곤란하면 5센티미터 이하로 할 수 있다. 이 경우 그 틈 사이로 물체 등이 떨어질 우려가 있는 곳에는 출입금지 등의 조치를 하여야 한다.&lt;br&gt; 4. 추락의 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업의 성질상 안전난간을 설치하는 것이 곤란한 경우, 작업의 필요상 임시로 안전난간을 해체할 때에 추락방호망을 설치하거나 근로자로 하여금 안전대를 사용하도록 하는 등 추락위험 방지 조치를 한 경우에는 그러하지 아니하다.&lt;br&gt; 5. 작업발판의 지지물은 하중에 의하여 파괴될 우려가 없는 것을 사용할 것&lt;br&gt;▶  6. &lt;strong&gt;작업발판재료는 뒤집히거나 떨어지지 않도록&lt;/strong&gt; &lt;strong&gt;둘 이상의 지지물에&lt;/strong&gt; 연결하거나 고정시킬 것&lt;br&gt; 7. 작업발판을 작업에 따라 이동시킬 경우에는 위험 방지에 필요한 조치를 할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제56조 — 작업발판의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;한 점만 고정하면 그 점을 축으로 돌아간다&lt;/strong&gt; — 그래서 &lt;strong&gt;둘 이상&lt;/strong&gt;이라야 한다. &lt;strong&gt;「하나 이상」과 「둘 이상」&lt;/strong&gt;을 바꿔 놓는 것이 이 유형의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;둘 이상의 지지물에 고정&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C56%EC%A1%B0" target="_blank"&gt;제56조(작업발판의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 비계(달비계, 달대비계 및 말비계는 제외한다)의 높이가 2미터 이상인 작업장소에 다음 각 호의 기준에 맞는 작업발판을 설치하여야 한다. &amp;lt;개정 2012.5.31, 2017.12.28&amp;gt;&lt;br&gt; 1. 발판재료는 작업할 때의 하중을 견딜 수 있도록 견고한 것으로 할 것&lt;br&gt; 2. 작업발판의 폭은 40센티미터 이상으로 하고, 발판재료 간의 틈은 3센티미터 이하로 할 것. 다만, 외줄비계의 경우에는 고용노동부장관이 별도로 정하는 기준에 따른다.&lt;br&gt; 3. 제2호에도 불구하고 선박 및 보트 건조작업의 경우 선박블록 또는 엔진실 등의 좁은 작업공간에 작업발판을 설치하기 위하여 필요하면 작업발판의 폭을 30센티미터 이상으로 할 수 있고, 걸침비계의 경우 강관기둥 때문에 발판재료 간의 틈을 3센티미터 이하로 유지하기 곤란하면 5센티미터 이하로 할 수 있다. 이 경우 그 틈 사이로 물체 등이 떨어질 우려가 있는 곳에는 출입금지 등의 조치를 하여야 한다.&lt;br&gt; 4. 추락의 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업의 성질상 안전난간을 설치하는 것이 곤란한 경우, 작업의 필요상 임시로 안전난간을 해체할 때에 추락방호망을 설치하거나 근로자로 하여금 안전대를 사용하도록 하는 등 추락위험 방지 조치를 한 경우에는 그러하지 아니하다.&lt;br&gt; 5. 작업발판의 지지물은 하중에 의하여 파괴될 우려가 없는 것을 사용할 것&lt;br&gt;▶  6. &lt;strong&gt;작업발판재료는 뒤집히거나 떨어지지 않도록&lt;/strong&gt; &lt;strong&gt;둘 이상의 지지물에&lt;/strong&gt; 연결하거나 고정시킬 것&lt;br&gt; 7. 작업발판을 작업에 따라 이동시킬 경우에는 위험 방지에 필요한 조치를 할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -16038,7 +16042,7 @@
       </c>
       <c r="AI116" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;건설업 산업안전보건관리비 계상 및 사용기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;5 ~ 50억원 구간에만 기초액이 붙는&lt;/strong&gt; 까닭은 &lt;strong&gt;비율만 쓰면 구간 경계에서 금액이 뚝 떨어지기&lt;/strong&gt; 때문이다. &lt;strong&gt;기초액은 그 계단을 메우는 값&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;일반(갑) 5~50억은 1.86 [%] + 534.9만원&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;고용노동부 고시 제2024-53호(2025. 1. 1. 시행)&lt;/u&gt;로 &lt;u&gt;공사종류가 「건축공사 · 토목공사 · 중건설공사 · 특수건설공사」 넷으로 개편&lt;/u&gt; 되어 &lt;u&gt;「일반건설공사(갑)·(을)」 구분이 폐지&lt;/u&gt; 되었다. 지금은 &lt;u&gt;건축공사 5 ~ 50억원 미만이 2.53 [%] + 5,499,000원&lt;/u&gt;처럼 새 표를 쓴다. 이 문항은 &lt;u&gt;옛 기준으로 푸는 문항&lt;/u&gt;이다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;건설업 산업안전보건관리비 계상 및 사용기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;5 ~ 50억원 구간에만 기초액이 붙는&lt;/strong&gt; 까닭은 &lt;strong&gt;비율만 쓰면 구간 경계에서 금액이 뚝 떨어지기&lt;/strong&gt; 때문이다. &lt;strong&gt;기초액은 그 계단을 메우는 값&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;일반(갑) 5~50억은 1.86 [%] + 534.9만원&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;고용노동부 고시 제2024-53호(2025. 1. 1. 시행)&lt;/u&gt;로 &lt;u&gt;공사종류가 「건축공사 · 토목공사 · 중건설공사 · 특수건설공사」 넷으로 개편&lt;/u&gt;되어 &lt;u&gt;「일반건설공사(갑)·(을)」 구분이 폐지&lt;/u&gt; 되었다. 지금은 &lt;u&gt;건축공사 5 ~ 50억원 미만이 2.53 [%] + 5,499,000원&lt;/u&gt;처럼 새 표를 쓴다. 이 문항은 &lt;u&gt;옛 기준으로 푸는 문항&lt;/u&gt;이다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16544,17 +16548,17 @@
       </c>
       <c r="AG120" s="32" t="inlineStr">
         <is>
-          <t>끊어진 소선은 &lt;strong&gt;10 [%] 이상&lt;/strong&gt; 이라야 사용 금지다. &lt;strong&gt;8 [%] 는 아직 쓸 수&lt;/strong&gt; 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용 금지 기준 (규칙 제166조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용 금지 사유&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기와의 대응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④가 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수가 10 [%] 이상인 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①은 8 [%] 라 아직 쓸 수 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소가 공칭지름의 7 [%] 를 초과하는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②는 8 [%] 라 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③이 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열과 전기충격에 의해 손상된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>끊어진 소선은 &lt;strong&gt;10 [%] 이상&lt;/strong&gt;이라야 사용 금지다. &lt;strong&gt;8 [%]는 아직 쓸 수&lt;/strong&gt; 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용 금지 기준 (규칙 제166조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용 금지 사유&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기와의 대응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④가 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수가 10 [%] 이상인 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①은 8 [%] 라 아직 쓸 수 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소가 공칭지름의 7 [%]를 초과하는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②는 8 [%] 라 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③이 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열과 전기충격에 의해 손상된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH120" s="32" t="inlineStr">
         <is>
-          <t>② 지름의 감소가 8 [%] 면 7 [%] 를 넘으므로 사용 금지다.&lt;br&gt;③ 심하게 부식된 것은 사용 금지다.&lt;br&gt;④ 이음매가 있는 것도 사용 금지다.</t>
+          <t>② 지름의 감소가 8 [%] 면 7 [%]를 넘으므로 사용 금지다.&lt;br&gt;③ 심하게 부식된 것은 사용 금지다.&lt;br&gt;④ 이음매가 있는 것도 사용 금지다.</t>
         </is>
       </c>
       <c r="AI120" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제166조 — 와이어로프의 사용 금지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;소선 10 [%], 지름 7 [%]&lt;/strong&gt; 두 숫자를 짝으로 잡는다. &lt;strong&gt;8 [%] 라는 같은 값이 하나는 통과, 하나는 불합격&lt;/strong&gt;이 되도록 짜여 있어 두 기준을 정확히 알아야 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;소선 10 [%], 지름 7 [%]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C166%EC%A1%B0" target="_blank"&gt;제166조(이음매가 있는 와이어로프 등의 사용 금지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;제166조(이음매가 있는 와이어로프 등의 사용 금지) 와이어 로프의 사용에 관하여는 제63조제1항제1호를 준용한다. 이 경우 "달비계"는 "양중기"로 본다. &amp;lt;개정 2021.11.19, 2022.10.18&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제166조 — 와이어로프의 사용 금지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;소선 10 [%], 지름 7 [%]&lt;/strong&gt; 두 숫자를 짝으로 잡는다. &lt;strong&gt;8 [%]라는 같은 값이 하나는 통과, 하나는 불합격&lt;/strong&gt;이 되도록 짜여 있어 두 기준을 정확히 알아야 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;소선 10 [%], 지름 7 [%]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C166%EC%A1%B0" target="_blank"&gt;제166조(이음매가 있는 와이어로프 등의 사용 금지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;제166조(이음매가 있는 와이어로프 등의 사용 금지) 와이어 로프의 사용에 관하여는 제63조제1항제1호를 준용한다. 이 경우 "달비계"는 "양중기"로 본다. &amp;lt;개정 2021.11.19, 2022.10.18&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -16673,17 +16677,17 @@
       </c>
       <c r="AG121" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;사각 또는 마름모로 10 [cm] 이하&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;추락방호망의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그물코&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사각 또는 마름모로 10 [cm] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설치 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업면에서 10 [m] 를 초과하지 않게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내민 길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;벽면에서 3 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;처짐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;짧은 변 길이의 12 [%] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;겹침 폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.75 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;사각 또는 마름모로 10 [cm] 이하&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;추락방호망의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그물코&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사각 또는 마름모로 10 [cm] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설치 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업면에서 10 [m]를 초과하지 않게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내민 길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;벽면에서 3 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;처짐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;짧은 변 길이의 12 [%] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;겹침 폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.75 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH121" s="32" t="inlineStr">
         <is>
-          <t>① 5 [cm] 는 방망사 규격에 있는 값이지만 그물코 기준은 10 [cm] 이하다.&lt;br&gt;③ 15 [cm] 라는 기준은 없다.&lt;br&gt;④ 20 [cm] 도 없다.</t>
+          <t>① 5 [cm]는 방망사 규격에 있는 값이지만 그물코 기준은 10 [cm] 이하다.&lt;br&gt;③ 15 [cm]라는 기준은 없다.&lt;br&gt;④ 20 [cm] 도 없다.</t>
         </is>
       </c>
       <c r="AI121" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제42조 — 추락방호망의 설치&lt;/strong&gt;&lt;br&gt;다섯 숫자를 묶어 둔다 — &lt;strong&gt;그물코 10 [cm] · 설치 높이 10 [m] · 내민 길이 3 [m] · 처짐 12 [%] · 겹침 0.75 [m]&lt;/strong&gt;. &lt;strong&gt;그물코가 10 [cm] 를 넘으면 사람이 빠져나간다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;그물코는 10 [cm] 이하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C42%EC%A1%B0" target="_blank"&gt;제42조(추락의 방지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 근로자가 추락하거나 넘어질 위험이 있는 장소[작업발판의 끝ㆍ개구부(開口部) 등을 제외한다]또는 기계ㆍ설비ㆍ선박블록 등에서 작업을 할 때에 근로자가 위험해질 우려가 있는 경우 비계(飛階)를 조립하는 등의 방법으로 작업발판을 설치하여야 한다.&lt;br&gt;② 사업주는 제1항에 따른 작업발판을 설치하기 곤란한 경우 다음 각 호의 기준에 맞는 추락방호망을 설치해야 한다. 다만, 추락방호망을 설치하기 곤란한 경우에는 근로자에게 안전대를 착용하도록 하는 등 추락위험을 방지하기 위해 필요한 조치를 해야 한다. &amp;lt;개정 2017.12.28, 2021.5.28&amp;gt;&lt;br&gt; 1. 추락방호망의 설치위치는 가능하면 작업면으로부터 가까운 지점에 설치하여야 하며, 작업면으로부터 망의 설치지점까지의 수직거리는 10미터를 초과하지 아니할 것&lt;br&gt; 2. 추락방호망은 수평으로 설치하고, 망의 처짐은 짧은 변 길이의 12퍼센트 이상이 되도록 할 것&lt;br&gt;▶  3. 건축물 등의 바깥쪽으로 설치하는 경우 추락방호망의 내민 길이는 벽면으로부터 3미터 이상 되도록 할 것. 다만, 그물코가 20밀리미터 이하인 추락방호망을 사용한 경우에는 제14조제3항에 따른 낙하물 방지망을 설치한 것으로 본다.&lt;br&gt;③ 사업주는 추락방호망을 설치하는 경우에는 한국산업표준에서 정하는 성능기준에 적합한 추락방호망을 사용하여야 한다. &amp;lt;신설 2017.12.28, 2022.10.18&amp;gt;&lt;br&gt;④ 사업주는 제1항 및 제2항에도 불구하고 작업발판 및 추락방호망을 설치하기 곤란한 경우에는 근로자로 하여금 3개 이상의 버팀대를 가지고 지면으로부터 안정적으로 세울 수 있는 구조를 갖춘 이동식 사다리를 사용하여 작업을 하게 할 수 있다. 이 경우 사업주는 근로자가 다음 각 호의 사항을 준수하도록 조치해야 한다. &amp;lt;신설 2024.6.28&amp;gt;&lt;br&gt; 1. 평탄하고 견고하며 미끄럽지 않은 바닥에 이동식 사다리를 설치할 것&lt;br&gt; 2. 이동식 사다리의 넘어짐을 방지하기 위해 다음 각 목의 어느 하나 이상에 해당하는 조치를 할 것&lt;br&gt; 가. 이동식 사다리를 견고한 시설물에 연결하여 고정할 것&lt;br&gt; 나. 아웃트리거(outrigger, 전도방지용 지지대)를 설치하거나 아웃트리거가 붙어있는 이동식 사다리를 설치할 것&lt;br&gt; 다. 이동식 사다리를 다른 근로자가 지지하여 넘어지지 않도록 할 것&lt;br&gt; 3. 이동식 사다리의 제조사가 정하여 표시한 이동식 사다리의 최대사용하중을 초과하지 않는 범위 내에서만 사용할 것&lt;br&gt; 4. 이동식 사다리를 설치한 바닥면에서 높이 3.5미터 이하의 장소에서만 작업할 것&lt;br&gt; 5. 이동식 사다리의 최상부 발판 및 그 하단 디딤대에 올라서서 작업하지 않을 것. 다만, 높이 1미터 이하의 사다리는 제외한다.&lt;br&gt; 6. 안전모를 착용하되, 작업 높이가 2미터 이상인 경우에는 안전모와 안전대를 함께 착용할 것&lt;br&gt; 7. 이동식 사다리 사용 전 변형 및 이상 유무 등을 점검하여 이상이 발견되면 즉시 수리하거나 그 밖에 필요한 조치를 할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제42조 — 추락방호망의 설치&lt;/strong&gt;&lt;br&gt;다섯 숫자를 묶어 둔다 — &lt;strong&gt;그물코 10 [cm] · 설치 높이 10 [m] · 내민 길이 3 [m] · 처짐 12 [%] · 겹침 0.75 [m]&lt;/strong&gt;. &lt;strong&gt;그물코가 10 [cm]를 넘으면 사람이 빠져나간다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;그물코는 10 [cm] 이하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C42%EC%A1%B0" target="_blank"&gt;제42조(추락의 방지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 근로자가 추락하거나 넘어질 위험이 있는 장소[작업발판의 끝ㆍ개구부(開口部) 등을 제외한다]또는 기계ㆍ설비ㆍ선박블록 등에서 작업을 할 때에 근로자가 위험해질 우려가 있는 경우 비계(飛階)를 조립하는 등의 방법으로 작업발판을 설치하여야 한다.&lt;br&gt;② 사업주는 제1항에 따른 작업발판을 설치하기 곤란한 경우 다음 각 호의 기준에 맞는 추락방호망을 설치해야 한다. 다만, 추락방호망을 설치하기 곤란한 경우에는 근로자에게 안전대를 착용하도록 하는 등 추락위험을 방지하기 위해 필요한 조치를 해야 한다. &amp;lt;개정 2017.12.28, 2021.5.28&amp;gt;&lt;br&gt; 1. 추락방호망의 설치위치는 가능하면 작업면으로부터 가까운 지점에 설치하여야 하며, 작업면으로부터 망의 설치지점까지의 수직거리는 10미터를 초과하지 아니할 것&lt;br&gt; 2. 추락방호망은 수평으로 설치하고, 망의 처짐은 짧은 변 길이의 12퍼센트 이상이 되도록 할 것&lt;br&gt;▶  3. 건축물 등의 바깥쪽으로 설치하는 경우 추락방호망의 내민 길이는 벽면으로부터 3미터 이상 되도록 할 것. 다만, 그물코가 20밀리미터 이하인 추락방호망을 사용한 경우에는 제14조제3항에 따른 낙하물 방지망을 설치한 것으로 본다.&lt;br&gt;③ 사업주는 추락방호망을 설치하는 경우에는 한국산업표준에서 정하는 성능기준에 적합한 추락방호망을 사용하여야 한다. &amp;lt;신설 2017.12.28, 2022.10.18&amp;gt;&lt;br&gt;④ 사업주는 제1항 및 제2항에도 불구하고 작업발판 및 추락방호망을 설치하기 곤란한 경우에는 근로자로 하여금 3개 이상의 버팀대를 가지고 지면으로부터 안정적으로 세울 수 있는 구조를 갖춘 이동식 사다리를 사용하여 작업을 하게 할 수 있다. 이 경우 사업주는 근로자가 다음 각 호의 사항을 준수하도록 조치해야 한다. &amp;lt;신설 2024.6.28&amp;gt;&lt;br&gt; 1. 평탄하고 견고하며 미끄럽지 않은 바닥에 이동식 사다리를 설치할 것&lt;br&gt; 2. 이동식 사다리의 넘어짐을 방지하기 위해 다음 각 목의 어느 하나 이상에 해당하는 조치를 할 것&lt;br&gt; 가. 이동식 사다리를 견고한 시설물에 연결하여 고정할 것&lt;br&gt; 나. 아웃트리거(outrigger, 전도방지용 지지대)를 설치하거나 아웃트리거가 붙어있는 이동식 사다리를 설치할 것&lt;br&gt; 다. 이동식 사다리를 다른 근로자가 지지하여 넘어지지 않도록 할 것&lt;br&gt; 3. 이동식 사다리의 제조사가 정하여 표시한 이동식 사다리의 최대사용하중을 초과하지 않는 범위 내에서만 사용할 것&lt;br&gt; 4. 이동식 사다리를 설치한 바닥면에서 높이 3.5미터 이하의 장소에서만 작업할 것&lt;br&gt; 5. 이동식 사다리의 최상부 발판 및 그 하단 디딤대에 올라서서 작업하지 않을 것. 다만, 높이 1미터 이하의 사다리는 제외한다.&lt;br&gt; 6. 안전모를 착용하되, 작업 높이가 2미터 이상인 경우에는 안전모와 안전대를 함께 착용할 것&lt;br&gt; 7. 이동식 사다리 사용 전 변형 및 이상 유무 등을 점검하여 이상이 발견되면 즉시 수리하거나 그 밖에 필요한 조치를 할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -16807,7 +16811,7 @@
       </c>
       <c r="AH122" s="32" t="inlineStr">
         <is>
-          <t>① 한 꼬임에서 끊어진 소선이 10 [%] 이상인 것은 사용 금지다.&lt;br&gt;② 지름의 감소가 공칭지름의 7 [%] 를 초과하는 것도 그렇다.&lt;br&gt;③ 심하게 변형되거나 부식된 것도 그렇다.</t>
+          <t>① 한 꼬임에서 끊어진 소선이 10 [%] 이상인 것은 사용 금지다.&lt;br&gt;② 지름의 감소가 공칭지름의 7 [%]를 초과하는 것도 그렇다.&lt;br&gt;③ 심하게 변형되거나 부식된 것도 그렇다.</t>
         </is>
       </c>
       <c r="AI122" s="32" t="inlineStr">
